--- a/backend/data/financials_by_company/1BC8.MI.xlsx
+++ b/backend/data/financials_by_company/1BC8.MI.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR5"/>
+  <dimension ref="A1:AR6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -642,179 +642,101 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="D2" t="n">
-        <v>510227000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>245498000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>140320000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>5167395000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>510227000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>369907000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-6039000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>24854000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>18815000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>245498000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>245498000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>5954786000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>126000000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>126000000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="T2" t="n">
-        <v>245498000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>245498000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>245498000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>647000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>244851000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>244851000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>100202000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>345053000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>351000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-6039000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>24854000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>18815000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>350976000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>787391000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>169138000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>76170000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>76170000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
-        <v>1138367000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>5167395000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>6305762000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>6305762000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="n">
+        <v>107282000</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="n">
+        <v>64120000</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.291</v>
+        <v>0.284</v>
       </c>
       <c r="D3" t="n">
-        <v>516057000</v>
+        <v>468999000</v>
       </c>
       <c r="E3" t="n">
-        <v>265512000</v>
+        <v>251118000</v>
       </c>
       <c r="F3" t="n">
-        <v>126621000</v>
+        <v>112062000</v>
       </c>
       <c r="G3" t="n">
-        <v>5300840000</v>
+        <v>4974795000</v>
       </c>
       <c r="H3" t="n">
-        <v>516057000</v>
+        <v>468999000</v>
       </c>
       <c r="I3" t="n">
-        <v>389436000</v>
+        <v>356937000</v>
       </c>
       <c r="J3" t="n">
-        <v>-8054000</v>
+        <v>-4938000</v>
       </c>
       <c r="K3" t="n">
-        <v>14959000</v>
+        <v>6450000</v>
       </c>
       <c r="L3" t="n">
-        <v>6905000</v>
+        <v>1512000</v>
       </c>
       <c r="M3" t="n">
-        <v>265512000</v>
+        <v>251118000</v>
       </c>
       <c r="N3" t="n">
-        <v>265512000</v>
+        <v>251118000</v>
       </c>
       <c r="O3" t="n">
-        <v>6041319000</v>
+        <v>5673741000</v>
       </c>
       <c r="P3" t="n">
         <v>126000000</v>
@@ -823,132 +745,130 @@
         <v>126000000</v>
       </c>
       <c r="R3" t="n">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="S3" t="n">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="T3" t="n">
-        <v>265512000</v>
+        <v>251118000</v>
       </c>
       <c r="U3" t="n">
-        <v>265512000</v>
+        <v>251118000</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>265512000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
+        <v>251118000</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>265512000</v>
+        <v>251118000</v>
       </c>
       <c r="Z3" t="n">
-        <v>265512000</v>
+        <v>251118000</v>
       </c>
       <c r="AA3" t="n">
-        <v>108965000</v>
+        <v>99369000</v>
       </c>
       <c r="AB3" t="n">
-        <v>374477000</v>
+        <v>350487000</v>
       </c>
       <c r="AC3" t="n">
-        <v>872000</v>
+        <v>991000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-8054000</v>
+        <v>-4938000</v>
       </c>
       <c r="AE3" t="n">
-        <v>14959000</v>
+        <v>6450000</v>
       </c>
       <c r="AF3" t="n">
-        <v>6905000</v>
+        <v>1512000</v>
       </c>
       <c r="AG3" t="n">
-        <v>381424000</v>
+        <v>354434000</v>
       </c>
       <c r="AH3" t="n">
-        <v>740479000</v>
+        <v>698946000</v>
       </c>
       <c r="AI3" t="n">
-        <v>152520000</v>
+        <v>136140000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>69405000</v>
+        <v>64728000</v>
       </c>
       <c r="AK3" t="n">
-        <v>69405000</v>
+        <v>64728000</v>
       </c>
       <c r="AL3" t="n">
-        <v>152520000</v>
+        <v>136140000</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>87722000</v>
+        <v>78775000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1121903000</v>
+        <v>1053380000</v>
       </c>
       <c r="AP3" t="n">
-        <v>5300840000</v>
+        <v>4974795000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6422743000</v>
+        <v>6028175000</v>
       </c>
       <c r="AR3" t="n">
-        <v>6422743000</v>
+        <v>6028175000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.284</v>
+        <v>0.291</v>
       </c>
       <c r="D4" t="n">
-        <v>468999000</v>
+        <v>516057000</v>
       </c>
       <c r="E4" t="n">
-        <v>251118000</v>
+        <v>265512000</v>
       </c>
       <c r="F4" t="n">
-        <v>112062000</v>
+        <v>126621000</v>
       </c>
       <c r="G4" t="n">
-        <v>4974795000</v>
+        <v>5300840000</v>
       </c>
       <c r="H4" t="n">
-        <v>468999000</v>
+        <v>516057000</v>
       </c>
       <c r="I4" t="n">
-        <v>356937000</v>
+        <v>389436000</v>
       </c>
       <c r="J4" t="n">
-        <v>-4938000</v>
+        <v>-8054000</v>
       </c>
       <c r="K4" t="n">
-        <v>6450000</v>
+        <v>14959000</v>
       </c>
       <c r="L4" t="n">
-        <v>1512000</v>
+        <v>6905000</v>
       </c>
       <c r="M4" t="n">
-        <v>251118000</v>
+        <v>265512000</v>
       </c>
       <c r="N4" t="n">
-        <v>251118000</v>
+        <v>265512000</v>
       </c>
       <c r="O4" t="n">
-        <v>5673741000</v>
+        <v>6041319000</v>
       </c>
       <c r="P4" t="n">
         <v>126000000</v>
@@ -957,130 +877,132 @@
         <v>126000000</v>
       </c>
       <c r="R4" t="n">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="S4" t="n">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="T4" t="n">
-        <v>251118000</v>
+        <v>265512000</v>
       </c>
       <c r="U4" t="n">
-        <v>251118000</v>
+        <v>265512000</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>251118000</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
+        <v>265512000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
       <c r="Y4" t="n">
-        <v>251118000</v>
+        <v>265512000</v>
       </c>
       <c r="Z4" t="n">
-        <v>251118000</v>
+        <v>265512000</v>
       </c>
       <c r="AA4" t="n">
-        <v>99369000</v>
+        <v>108965000</v>
       </c>
       <c r="AB4" t="n">
-        <v>350487000</v>
+        <v>374477000</v>
       </c>
       <c r="AC4" t="n">
-        <v>991000</v>
+        <v>872000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-4938000</v>
+        <v>-8054000</v>
       </c>
       <c r="AE4" t="n">
-        <v>6450000</v>
+        <v>14959000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1512000</v>
+        <v>6905000</v>
       </c>
       <c r="AG4" t="n">
-        <v>354434000</v>
+        <v>381424000</v>
       </c>
       <c r="AH4" t="n">
-        <v>698946000</v>
+        <v>740479000</v>
       </c>
       <c r="AI4" t="n">
-        <v>136140000</v>
+        <v>152520000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>64728000</v>
+        <v>69405000</v>
       </c>
       <c r="AK4" t="n">
-        <v>64728000</v>
+        <v>69405000</v>
       </c>
       <c r="AL4" t="n">
-        <v>136140000</v>
+        <v>152520000</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>78775000</v>
+        <v>87722000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1053380000</v>
+        <v>1121903000</v>
       </c>
       <c r="AP4" t="n">
-        <v>4974795000</v>
+        <v>5300840000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6028175000</v>
+        <v>6422743000</v>
       </c>
       <c r="AR4" t="n">
-        <v>6028175000</v>
+        <v>6422743000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.278</v>
+        <v>0.290396</v>
       </c>
       <c r="D5" t="n">
-        <v>430139000</v>
+        <v>510227000</v>
       </c>
       <c r="E5" t="n">
-        <v>231446000</v>
+        <v>245498000</v>
       </c>
       <c r="F5" t="n">
-        <v>103003000</v>
+        <v>140320000</v>
       </c>
       <c r="G5" t="n">
-        <v>4385481000</v>
+        <v>5167395000</v>
       </c>
       <c r="H5" t="n">
-        <v>430139000</v>
+        <v>510227000</v>
       </c>
       <c r="I5" t="n">
-        <v>327136000</v>
+        <v>369907000</v>
       </c>
       <c r="J5" t="n">
-        <v>-5221000</v>
+        <v>-6039000</v>
       </c>
       <c r="K5" t="n">
-        <v>6636000</v>
+        <v>24854000</v>
       </c>
       <c r="L5" t="n">
-        <v>1415000</v>
+        <v>18815000</v>
       </c>
       <c r="M5" t="n">
-        <v>231446000</v>
+        <v>245498000</v>
       </c>
       <c r="N5" t="n">
-        <v>231446000</v>
+        <v>245498000</v>
       </c>
       <c r="O5" t="n">
-        <v>4980536000</v>
+        <v>5954786000</v>
       </c>
       <c r="P5" t="n">
         <v>126000000</v>
@@ -1089,83 +1011,211 @@
         <v>126000000</v>
       </c>
       <c r="R5" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="S5" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="T5" t="n">
-        <v>231446000</v>
+        <v>245498000</v>
       </c>
       <c r="U5" t="n">
-        <v>231446000</v>
+        <v>245498000</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>231446000</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
+        <v>245498000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>647000</v>
+      </c>
       <c r="Y5" t="n">
-        <v>231446000</v>
+        <v>244851000</v>
       </c>
       <c r="Z5" t="n">
-        <v>231446000</v>
+        <v>244851000</v>
       </c>
       <c r="AA5" t="n">
-        <v>89054000</v>
+        <v>100202000</v>
       </c>
       <c r="AB5" t="n">
-        <v>320500000</v>
+        <v>345053000</v>
       </c>
       <c r="AC5" t="n">
-        <v>768000</v>
+        <v>351000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-5221000</v>
+        <v>-6039000</v>
       </c>
       <c r="AE5" t="n">
-        <v>6636000</v>
+        <v>24854000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1415000</v>
+        <v>18815000</v>
       </c>
       <c r="AG5" t="n">
-        <v>324953000</v>
+        <v>350976000</v>
       </c>
       <c r="AH5" t="n">
-        <v>595055000</v>
+        <v>787391000</v>
       </c>
       <c r="AI5" t="n">
-        <v>107282000</v>
+        <v>169138000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>61210000</v>
+        <v>76170000</v>
       </c>
       <c r="AK5" t="n">
-        <v>61210000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>107282000</v>
-      </c>
+        <v>76170000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
-      <c r="AN5" t="n">
-        <v>64120000</v>
-      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>920008000</v>
+        <v>1138367000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4385481000</v>
+        <v>5167395000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5305489000</v>
+        <v>6305762000</v>
       </c>
       <c r="AR5" t="n">
-        <v>5305489000</v>
+        <v>6305762000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="D6" t="n">
+        <v>510841000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>229211000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>159268000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5214363000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>510841000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>351573000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-11099000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27376000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>16277000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>229211000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>229211000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>6071212000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>126000000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>126000000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="T6" t="n">
+        <v>229211000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>229211000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>229211000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>887000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>228324000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>228324000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>95873000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>324197000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>634000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-11099000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>27376000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>16277000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>334662000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>856849000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>181904000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>85095000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>85095000</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>1191511000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>5214363000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>6405874000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>6405874000</v>
       </c>
     </row>
   </sheetData>
@@ -1179,7 +1229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ5"/>
+  <dimension ref="A1:BZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1571,239 +1621,95 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>126000000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>126000000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>812251000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>902373000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2496904000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1029935000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>902373000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>226793000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1911446000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2315626000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1915070000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3624000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1911446000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1716516000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>68930000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>126000000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>126000000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2302211000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>694043000</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>11716000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3604000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>35180000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>47291000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>568761000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>164581000</v>
-      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>404180000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>13098000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1608168000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>243490000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>62212000</v>
-      </c>
+        <v>310941000</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>181278000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>123118000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>18482000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>903930000</v>
-      </c>
+        <v>34537000</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>1057000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>75895000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>826978000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>4217281000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1579178000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>3690000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8528000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>2719000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>2719000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1009073000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>152214000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>856859000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>486386000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-347311000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>833697000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>10479000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>364011000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>249412000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>209795000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>2638103000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>4180000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>7330000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>373322000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>-20634000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>11216000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>382740000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>338887000</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>33554000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>1153755000</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>-17335000</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>1171090000</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>727075000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>83960000</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>643115000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>185700000</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>457415000</v>
-      </c>
+        <v>606000</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>126000000</v>
@@ -1812,46 +1718,44 @@
         <v>126000000</v>
       </c>
       <c r="D3" t="n">
-        <v>104758000</v>
+        <v>143685000</v>
       </c>
       <c r="E3" t="n">
-        <v>734040000</v>
+        <v>523150000</v>
       </c>
       <c r="F3" t="n">
-        <v>892814000</v>
+        <v>884421000</v>
       </c>
       <c r="G3" t="n">
-        <v>2283126000</v>
+        <v>1911594000</v>
       </c>
       <c r="H3" t="n">
-        <v>1100173000</v>
+        <v>888060000</v>
       </c>
       <c r="I3" t="n">
-        <v>892814000</v>
+        <v>884421000</v>
       </c>
       <c r="J3" t="n">
-        <v>193526000</v>
+        <v>149875000</v>
       </c>
       <c r="K3" t="n">
-        <v>1742612000</v>
+        <v>1538319000</v>
       </c>
       <c r="L3" t="n">
-        <v>2266728000</v>
+        <v>1800214000</v>
       </c>
       <c r="M3" t="n">
-        <v>1742612000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
+        <v>1538319000</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>1742612000</v>
+        <v>1538319000</v>
       </c>
       <c r="P3" t="n">
-        <v>1549699000</v>
+        <v>1372091000</v>
       </c>
       <c r="Q3" t="n">
-        <v>66913000</v>
+        <v>40228000</v>
       </c>
       <c r="R3" t="n">
         <v>126000000</v>
@@ -1860,186 +1764,182 @@
         <v>126000000</v>
       </c>
       <c r="T3" t="n">
-        <v>2060577000</v>
+        <v>1909553000</v>
       </c>
       <c r="U3" t="n">
-        <v>784876000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1000</v>
-      </c>
+        <v>464919000</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>17283000</v>
+        <v>7928000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2516000</v>
+        <v>2224000</v>
       </c>
       <c r="AA3" t="n">
-        <v>54647000</v>
+        <v>50424000</v>
       </c>
       <c r="AB3" t="n">
-        <v>38997000</v>
+        <v>33452000</v>
       </c>
       <c r="AC3" t="n">
-        <v>660452000</v>
+        <v>360346000</v>
       </c>
       <c r="AD3" t="n">
-        <v>136336000</v>
+        <v>98451000</v>
       </c>
       <c r="AE3" t="n">
-        <v>524116000</v>
+        <v>261895000</v>
       </c>
       <c r="AF3" t="n">
-        <v>10883000</v>
+        <v>10371000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1275701000</v>
+        <v>1444634000</v>
       </c>
       <c r="AH3" t="n">
-        <v>73588000</v>
+        <v>162804000</v>
       </c>
       <c r="AI3" t="n">
-        <v>57190000</v>
+        <v>51424000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>16398000</v>
+        <v>111380000</v>
       </c>
       <c r="AK3" t="n">
-        <v>130132000</v>
+        <v>128957000</v>
       </c>
       <c r="AL3" t="n">
-        <v>19020000</v>
+        <v>30767000</v>
       </c>
       <c r="AM3" t="n">
-        <v>718073000</v>
+        <v>814698000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1069000</v>
+        <v>1746000</v>
       </c>
       <c r="AO3" t="n">
-        <v>87798000</v>
+        <v>113922000</v>
       </c>
       <c r="AP3" t="n">
-        <v>629206000</v>
+        <v>699030000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3803189000</v>
+        <v>3447872000</v>
       </c>
       <c r="AR3" t="n">
-        <v>1427315000</v>
+        <v>1115178000</v>
       </c>
       <c r="AS3" t="n">
-        <v>3794000</v>
+        <v>3209000</v>
       </c>
       <c r="AT3" t="n">
-        <v>10638000</v>
+        <v>9451000</v>
       </c>
       <c r="AU3" t="n">
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>380000</v>
+        <v>378000</v>
       </c>
       <c r="AW3" t="n">
-        <v>380000</v>
+        <v>378000</v>
       </c>
       <c r="AX3" t="n">
-        <v>32497000</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>32497000</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>849798000</v>
+        <v>653898000</v>
       </c>
       <c r="BA3" t="n">
-        <v>117468000</v>
+        <v>99701000</v>
       </c>
       <c r="BB3" t="n">
-        <v>732330000</v>
+        <v>554197000</v>
       </c>
       <c r="BC3" t="n">
-        <v>441825000</v>
+        <v>365512000</v>
       </c>
       <c r="BD3" t="n">
-        <v>-305682000</v>
+        <v>-273120000</v>
       </c>
       <c r="BE3" t="n">
-        <v>747507000</v>
+        <v>638632000</v>
       </c>
       <c r="BF3" t="n">
-        <v>9229000</v>
+        <v>20819000</v>
       </c>
       <c r="BG3" t="n">
-        <v>320243000</v>
+        <v>261691000</v>
       </c>
       <c r="BH3" t="n">
-        <v>217288000</v>
+        <v>189203000</v>
       </c>
       <c r="BI3" t="n">
-        <v>200747000</v>
+        <v>166919000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>2375874000</v>
+        <v>2332694000</v>
       </c>
       <c r="BK3" t="n">
-        <v>3089000</v>
+        <v>1824000</v>
       </c>
       <c r="BL3" t="n">
-        <v>3163000</v>
+        <v>846000</v>
       </c>
       <c r="BM3" t="n">
-        <v>467954000</v>
+        <v>607300000</v>
       </c>
       <c r="BN3" t="n">
-        <v>-23795000</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>28407000</v>
-      </c>
+        <v>-24052000</v>
+      </c>
+      <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="n">
-        <v>463342000</v>
+        <v>631352000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>244887000</v>
+        <v>196238000</v>
       </c>
       <c r="BR3" t="n">
-        <v>30486000</v>
+        <v>28382000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1157573000</v>
+        <v>1206399000</v>
       </c>
       <c r="BT3" t="n">
-        <v>-22269000</v>
+        <v>-23700000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1179842000</v>
+        <v>1230099000</v>
       </c>
       <c r="BV3" t="n">
-        <v>468722000</v>
+        <v>291705000</v>
       </c>
       <c r="BW3" t="n">
-        <v>32966000</v>
+        <v>62115000</v>
       </c>
       <c r="BX3" t="n">
-        <v>435756000</v>
+        <v>229590000</v>
       </c>
       <c r="BY3" t="n">
-        <v>86585000</v>
+        <v>30000000</v>
       </c>
       <c r="BZ3" t="n">
-        <v>349171000</v>
+        <v>199590000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>126000000</v>
@@ -2048,44 +1948,46 @@
         <v>126000000</v>
       </c>
       <c r="D4" t="n">
-        <v>143685000</v>
+        <v>104758000</v>
       </c>
       <c r="E4" t="n">
-        <v>523150000</v>
+        <v>734040000</v>
       </c>
       <c r="F4" t="n">
-        <v>884421000</v>
+        <v>892814000</v>
       </c>
       <c r="G4" t="n">
-        <v>1911594000</v>
+        <v>2283126000</v>
       </c>
       <c r="H4" t="n">
-        <v>888060000</v>
+        <v>1100173000</v>
       </c>
       <c r="I4" t="n">
-        <v>884421000</v>
+        <v>892814000</v>
       </c>
       <c r="J4" t="n">
-        <v>149875000</v>
+        <v>193526000</v>
       </c>
       <c r="K4" t="n">
-        <v>1538319000</v>
+        <v>1742612000</v>
       </c>
       <c r="L4" t="n">
-        <v>1800214000</v>
+        <v>2266728000</v>
       </c>
       <c r="M4" t="n">
-        <v>1538319000</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
+        <v>1742612000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
       <c r="O4" t="n">
-        <v>1538319000</v>
+        <v>1742612000</v>
       </c>
       <c r="P4" t="n">
-        <v>1372091000</v>
+        <v>1549699000</v>
       </c>
       <c r="Q4" t="n">
-        <v>40228000</v>
+        <v>66913000</v>
       </c>
       <c r="R4" t="n">
         <v>126000000</v>
@@ -2094,182 +1996,186 @@
         <v>126000000</v>
       </c>
       <c r="T4" t="n">
-        <v>1909553000</v>
+        <v>2060577000</v>
       </c>
       <c r="U4" t="n">
-        <v>464919000</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
+        <v>784876000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1000</v>
+      </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>7928000</v>
+        <v>17283000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2224000</v>
+        <v>2516000</v>
       </c>
       <c r="AA4" t="n">
-        <v>50424000</v>
+        <v>54647000</v>
       </c>
       <c r="AB4" t="n">
-        <v>33452000</v>
+        <v>38997000</v>
       </c>
       <c r="AC4" t="n">
-        <v>360346000</v>
+        <v>660452000</v>
       </c>
       <c r="AD4" t="n">
-        <v>98451000</v>
+        <v>136336000</v>
       </c>
       <c r="AE4" t="n">
-        <v>261895000</v>
+        <v>524116000</v>
       </c>
       <c r="AF4" t="n">
-        <v>10371000</v>
+        <v>10883000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1444634000</v>
+        <v>1275701000</v>
       </c>
       <c r="AH4" t="n">
-        <v>162804000</v>
+        <v>73588000</v>
       </c>
       <c r="AI4" t="n">
-        <v>51424000</v>
+        <v>57190000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>111380000</v>
+        <v>16398000</v>
       </c>
       <c r="AK4" t="n">
-        <v>128957000</v>
+        <v>130132000</v>
       </c>
       <c r="AL4" t="n">
-        <v>30767000</v>
+        <v>19020000</v>
       </c>
       <c r="AM4" t="n">
-        <v>814698000</v>
+        <v>718073000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1746000</v>
+        <v>1069000</v>
       </c>
       <c r="AO4" t="n">
-        <v>113922000</v>
+        <v>87798000</v>
       </c>
       <c r="AP4" t="n">
-        <v>699030000</v>
+        <v>629206000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3447872000</v>
+        <v>3803189000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1115178000</v>
+        <v>1427315000</v>
       </c>
       <c r="AS4" t="n">
-        <v>3209000</v>
+        <v>3794000</v>
       </c>
       <c r="AT4" t="n">
-        <v>9451000</v>
+        <v>10638000</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>378000</v>
+        <v>380000</v>
       </c>
       <c r="AW4" t="n">
-        <v>378000</v>
+        <v>380000</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>32497000</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>32497000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>653898000</v>
+        <v>849798000</v>
       </c>
       <c r="BA4" t="n">
-        <v>99701000</v>
+        <v>117468000</v>
       </c>
       <c r="BB4" t="n">
-        <v>554197000</v>
+        <v>732330000</v>
       </c>
       <c r="BC4" t="n">
-        <v>365512000</v>
+        <v>441825000</v>
       </c>
       <c r="BD4" t="n">
-        <v>-273120000</v>
+        <v>-305682000</v>
       </c>
       <c r="BE4" t="n">
-        <v>638632000</v>
+        <v>747507000</v>
       </c>
       <c r="BF4" t="n">
-        <v>20819000</v>
+        <v>9229000</v>
       </c>
       <c r="BG4" t="n">
-        <v>261691000</v>
+        <v>320243000</v>
       </c>
       <c r="BH4" t="n">
-        <v>189203000</v>
+        <v>217288000</v>
       </c>
       <c r="BI4" t="n">
-        <v>166919000</v>
+        <v>200747000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>2332694000</v>
+        <v>2375874000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1824000</v>
+        <v>3089000</v>
       </c>
       <c r="BL4" t="n">
-        <v>846000</v>
+        <v>3163000</v>
       </c>
       <c r="BM4" t="n">
-        <v>607300000</v>
+        <v>467954000</v>
       </c>
       <c r="BN4" t="n">
-        <v>-24052000</v>
-      </c>
-      <c r="BO4" t="inlineStr"/>
+        <v>-23795000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>28407000</v>
+      </c>
       <c r="BP4" t="n">
-        <v>631352000</v>
+        <v>463342000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>196238000</v>
+        <v>244887000</v>
       </c>
       <c r="BR4" t="n">
-        <v>28382000</v>
+        <v>30486000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1206399000</v>
+        <v>1157573000</v>
       </c>
       <c r="BT4" t="n">
-        <v>-23700000</v>
+        <v>-22269000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1230099000</v>
+        <v>1179842000</v>
       </c>
       <c r="BV4" t="n">
-        <v>291705000</v>
+        <v>468722000</v>
       </c>
       <c r="BW4" t="n">
-        <v>62115000</v>
+        <v>32966000</v>
       </c>
       <c r="BX4" t="n">
-        <v>229590000</v>
+        <v>435756000</v>
       </c>
       <c r="BY4" t="n">
-        <v>30000000</v>
+        <v>86585000</v>
       </c>
       <c r="BZ4" t="n">
-        <v>199590000</v>
+        <v>349171000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>126000000</v>
@@ -2279,41 +2185,43 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>489228000</v>
+        <v>226793000</v>
       </c>
       <c r="F5" t="n">
-        <v>784606000</v>
+        <v>902373000</v>
       </c>
       <c r="G5" t="n">
-        <v>1698592000</v>
+        <v>1911446000</v>
       </c>
       <c r="H5" t="n">
-        <v>868448000</v>
+        <v>1029935000</v>
       </c>
       <c r="I5" t="n">
-        <v>784606000</v>
+        <v>902373000</v>
       </c>
       <c r="J5" t="n">
-        <v>143750000</v>
+        <v>226793000</v>
       </c>
       <c r="K5" t="n">
-        <v>1353114000</v>
+        <v>1911446000</v>
       </c>
       <c r="L5" t="n">
-        <v>1664055000</v>
+        <v>1911446000</v>
       </c>
       <c r="M5" t="n">
-        <v>1353114000</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
+        <v>1915070000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3624000</v>
+      </c>
       <c r="O5" t="n">
-        <v>1353114000</v>
+        <v>1911446000</v>
       </c>
       <c r="P5" t="n">
-        <v>1186886000</v>
+        <v>1716516000</v>
       </c>
       <c r="Q5" t="n">
-        <v>40228000</v>
+        <v>68930000</v>
       </c>
       <c r="R5" t="n">
         <v>126000000</v>
@@ -2322,170 +2230,398 @@
         <v>126000000</v>
       </c>
       <c r="T5" t="n">
-        <v>1666654000</v>
+        <v>2302211000</v>
       </c>
       <c r="U5" t="n">
-        <v>499533000</v>
+        <v>694043000</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>12994000</v>
+        <v>11716000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>754000</v>
+        <v>3604000</v>
       </c>
       <c r="AA5" t="n">
-        <v>22371000</v>
+        <v>35180000</v>
       </c>
       <c r="AB5" t="n">
-        <v>37271000</v>
+        <v>47291000</v>
       </c>
       <c r="AC5" t="n">
-        <v>411065000</v>
+        <v>164581000</v>
       </c>
       <c r="AD5" t="n">
-        <v>100124000</v>
+        <v>164581000</v>
       </c>
       <c r="AE5" t="n">
-        <v>310941000</v>
+        <v>404180000</v>
       </c>
       <c r="AF5" t="n">
-        <v>11379000</v>
+        <v>13098000</v>
       </c>
       <c r="AG5" t="n">
-        <v>1167121000</v>
+        <v>1608168000</v>
       </c>
       <c r="AH5" t="n">
-        <v>78163000</v>
+        <v>62212000</v>
       </c>
       <c r="AI5" t="n">
-        <v>43626000</v>
+        <v>62212000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34537000</v>
+        <v>181278000</v>
       </c>
       <c r="AK5" t="n">
-        <v>124552000</v>
+        <v>123118000</v>
       </c>
       <c r="AL5" t="n">
-        <v>27318000</v>
+        <v>18482000</v>
       </c>
       <c r="AM5" t="n">
-        <v>680879000</v>
+        <v>903930000</v>
       </c>
       <c r="AN5" t="n">
-        <v>606000</v>
+        <v>1057000</v>
       </c>
       <c r="AO5" t="n">
-        <v>75128000</v>
+        <v>75895000</v>
       </c>
       <c r="AP5" t="n">
-        <v>605145000</v>
+        <v>826978000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3019768000</v>
+        <v>4217281000</v>
       </c>
       <c r="AR5" t="n">
-        <v>984199000</v>
+        <v>1579178000</v>
       </c>
       <c r="AS5" t="n">
-        <v>3149000</v>
+        <v>3690000</v>
       </c>
       <c r="AT5" t="n">
-        <v>8924000</v>
+        <v>8528000</v>
       </c>
       <c r="AU5" t="n">
         <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>185000</v>
+        <v>2719000</v>
       </c>
       <c r="AW5" t="n">
-        <v>185000</v>
-      </c>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
+        <v>2719000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
       <c r="AZ5" t="n">
-        <v>568508000</v>
+        <v>1009073000</v>
       </c>
       <c r="BA5" t="n">
-        <v>98858000</v>
+        <v>152214000</v>
       </c>
       <c r="BB5" t="n">
-        <v>469650000</v>
+        <v>856859000</v>
       </c>
       <c r="BC5" t="n">
-        <v>342902000</v>
+        <v>486386000</v>
       </c>
       <c r="BD5" t="n">
-        <v>-228310000</v>
+        <v>-347311000</v>
       </c>
       <c r="BE5" t="n">
-        <v>571212000</v>
+        <v>833697000</v>
       </c>
       <c r="BF5" t="n">
-        <v>7463000</v>
+        <v>10479000</v>
       </c>
       <c r="BG5" t="n">
-        <v>229264000</v>
+        <v>364011000</v>
       </c>
       <c r="BH5" t="n">
-        <v>167775000</v>
+        <v>249412000</v>
       </c>
       <c r="BI5" t="n">
-        <v>166710000</v>
+        <v>209795000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>2035569000</v>
+        <v>2638103000</v>
       </c>
       <c r="BK5" t="n">
-        <v>4117000</v>
+        <v>4180000</v>
       </c>
       <c r="BL5" t="n">
-        <v>457000</v>
+        <v>7330000</v>
       </c>
       <c r="BM5" t="n">
-        <v>513586000</v>
+        <v>373322000</v>
       </c>
       <c r="BN5" t="n">
-        <v>-19085000</v>
-      </c>
-      <c r="BO5" t="inlineStr"/>
+        <v>-20634000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>11216000</v>
+      </c>
       <c r="BP5" t="n">
-        <v>532671000</v>
+        <v>382740000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>140550000</v>
+        <v>338887000</v>
       </c>
       <c r="BR5" t="n">
-        <v>14956000</v>
+        <v>33554000</v>
       </c>
       <c r="BS5" t="n">
-        <v>928724000</v>
+        <v>1153755000</v>
       </c>
       <c r="BT5" t="n">
-        <v>-25382000</v>
+        <v>-17335000</v>
       </c>
       <c r="BU5" t="n">
-        <v>954106000</v>
+        <v>1171090000</v>
       </c>
       <c r="BV5" t="n">
-        <v>433179000</v>
+        <v>727075000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1428000</v>
+        <v>83960000</v>
       </c>
       <c r="BX5" t="n">
-        <v>431751000</v>
-      </c>
-      <c r="BY5" t="inlineStr"/>
-      <c r="BZ5" t="inlineStr"/>
+        <v>643115000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>185700000</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>457415000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>126000000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>126000000</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>250263000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>873242000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2049518000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>959110000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>873242000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>250263000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2049518000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2049518000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2052255000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2737000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2049518000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1853528000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>69990000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>126000000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>126000000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2522400000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>791863000</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>12096000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>68509000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>45009000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>56856000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>181752000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>181752000</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>17065000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1730537000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>68511000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>68511000</v>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>128039000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>20013000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1063012000</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>104700000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>958312000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4574655000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1885008000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3546000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7991000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>307000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>307000</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>1176276000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>192413000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>983863000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>542266000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-405089000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>947355000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>46333000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>408829000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>278296000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>213897000</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>2689647000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>19912000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>2115000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>380060000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-21515000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>4506000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>397069000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>426205000</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>45760000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1348356000</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>-17084000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1365440000</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>467239000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>88468000</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>378771000</v>
+      </c>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2498,7 +2634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI5"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2675,420 +2811,461 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>469485000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-88666000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>643115000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>435756000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1445000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>205914000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-145969000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>35496000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-20732000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-88200000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-88200000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-206268000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>17466000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-42618000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>30382000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-73000000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-107983000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-107983000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-73133000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>15533000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-88666000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>558151000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-116204000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
-        <v>183092000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-150818000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>187054000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>103188000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>43668000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>5365000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>140320000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>140320000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>525000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>345053000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>5220000</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>357853000</v>
+        <v>34953000</v>
       </c>
       <c r="C3" t="n">
-        <v>-101178000</v>
+        <v>-81698000</v>
       </c>
       <c r="D3" t="n">
-        <v>435756000</v>
+        <v>229590000</v>
       </c>
       <c r="E3" t="n">
-        <v>229590000</v>
+        <v>431751000</v>
       </c>
       <c r="F3" t="n">
-        <v>1442000</v>
+        <v>5721000</v>
       </c>
       <c r="G3" t="n">
-        <v>204724000</v>
+        <v>-207882000</v>
       </c>
       <c r="H3" t="n">
-        <v>28246000</v>
+        <v>-100210000</v>
       </c>
       <c r="I3" t="n">
-        <v>189936000</v>
+        <v>27797000</v>
       </c>
       <c r="J3" t="n">
-        <v>-14925000</v>
+        <v>-5522000</v>
       </c>
       <c r="K3" t="n">
-        <v>-81900000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-81900000</v>
-      </c>
+        <v>-69300000</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>-282553000</v>
+        <v>-224323000</v>
       </c>
       <c r="N3" t="n">
-        <v>6084000</v>
+        <v>1021000</v>
       </c>
       <c r="O3" t="n">
-        <v>19179000</v>
+        <v>-78877000</v>
       </c>
       <c r="P3" t="n">
-        <v>60000000</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-40821000</v>
+        <v>-78877000</v>
       </c>
       <c r="R3" t="n">
-        <v>-223448000</v>
+        <v>-92165000</v>
       </c>
       <c r="S3" t="n">
-        <v>-223448000</v>
+        <v>-92165000</v>
       </c>
       <c r="T3" t="n">
-        <v>-84368000</v>
+        <v>-54302000</v>
       </c>
       <c r="U3" t="n">
-        <v>16810000</v>
+        <v>27396000</v>
       </c>
       <c r="V3" t="n">
-        <v>-101178000</v>
+        <v>-81698000</v>
       </c>
       <c r="W3" t="n">
-        <v>459031000</v>
+        <v>116651000</v>
       </c>
       <c r="X3" t="n">
-        <v>-113540000</v>
+        <v>-117812000</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>71982000</v>
+        <v>-242072000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-137287000</v>
+        <v>43393000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-97565000</v>
+        <v>56745000</v>
       </c>
       <c r="AC3" t="n">
-        <v>204113000</v>
+        <v>-93723000</v>
       </c>
       <c r="AD3" t="n">
-        <v>102721000</v>
+        <v>-248487000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-320000</v>
+        <v>14110000</v>
       </c>
       <c r="AF3" t="n">
-        <v>126621000</v>
+        <v>112062000</v>
       </c>
       <c r="AG3" t="n">
-        <v>126621000</v>
+        <v>112062000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-189000</v>
+        <v>-124000</v>
       </c>
       <c r="AI3" t="n">
-        <v>374477000</v>
+        <v>350487000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>34953000</v>
+        <v>357853000</v>
       </c>
       <c r="C4" t="n">
-        <v>-81698000</v>
+        <v>-101178000</v>
       </c>
       <c r="D4" t="n">
+        <v>435756000</v>
+      </c>
+      <c r="E4" t="n">
         <v>229590000</v>
       </c>
-      <c r="E4" t="n">
-        <v>431751000</v>
-      </c>
       <c r="F4" t="n">
-        <v>5721000</v>
+        <v>1442000</v>
       </c>
       <c r="G4" t="n">
-        <v>-207882000</v>
+        <v>204724000</v>
       </c>
       <c r="H4" t="n">
-        <v>-100210000</v>
+        <v>28246000</v>
       </c>
       <c r="I4" t="n">
-        <v>27797000</v>
+        <v>189936000</v>
       </c>
       <c r="J4" t="n">
-        <v>-5522000</v>
+        <v>-14925000</v>
       </c>
       <c r="K4" t="n">
-        <v>-69300000</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>-81900000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-81900000</v>
+      </c>
       <c r="M4" t="n">
-        <v>-224323000</v>
+        <v>-282553000</v>
       </c>
       <c r="N4" t="n">
-        <v>1021000</v>
+        <v>6084000</v>
       </c>
       <c r="O4" t="n">
-        <v>-78877000</v>
+        <v>19179000</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>60000000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-78877000</v>
+        <v>-40821000</v>
       </c>
       <c r="R4" t="n">
-        <v>-92165000</v>
+        <v>-223448000</v>
       </c>
       <c r="S4" t="n">
-        <v>-92165000</v>
+        <v>-223448000</v>
       </c>
       <c r="T4" t="n">
-        <v>-54302000</v>
+        <v>-84368000</v>
       </c>
       <c r="U4" t="n">
-        <v>27396000</v>
+        <v>16810000</v>
       </c>
       <c r="V4" t="n">
-        <v>-81698000</v>
+        <v>-101178000</v>
       </c>
       <c r="W4" t="n">
-        <v>116651000</v>
+        <v>459031000</v>
       </c>
       <c r="X4" t="n">
-        <v>-117812000</v>
+        <v>-113540000</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>-242072000</v>
+        <v>71982000</v>
       </c>
       <c r="AA4" t="n">
-        <v>43393000</v>
+        <v>-137287000</v>
       </c>
       <c r="AB4" t="n">
-        <v>56745000</v>
+        <v>-97565000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-93723000</v>
+        <v>204113000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-248487000</v>
+        <v>102721000</v>
       </c>
       <c r="AE4" t="n">
-        <v>14110000</v>
+        <v>-320000</v>
       </c>
       <c r="AF4" t="n">
-        <v>112062000</v>
+        <v>126621000</v>
       </c>
       <c r="AG4" t="n">
-        <v>112062000</v>
+        <v>126621000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-124000</v>
+        <v>-189000</v>
       </c>
       <c r="AI4" t="n">
-        <v>350487000</v>
+        <v>374477000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>226223000</v>
+        <v>469485000</v>
       </c>
       <c r="C5" t="n">
-        <v>-58269000</v>
+        <v>-88666000</v>
       </c>
       <c r="D5" t="n">
-        <v>431751000</v>
+        <v>643115000</v>
       </c>
       <c r="E5" t="n">
-        <v>363171000</v>
+        <v>435756000</v>
       </c>
       <c r="F5" t="n">
-        <v>6384000</v>
+        <v>1445000</v>
       </c>
       <c r="G5" t="n">
-        <v>62196000</v>
+        <v>205914000</v>
       </c>
       <c r="H5" t="n">
-        <v>-179356000</v>
+        <v>-145969000</v>
       </c>
       <c r="I5" t="n">
-        <v>-66976000</v>
+        <v>35496000</v>
       </c>
       <c r="J5" t="n">
-        <v>-6697000</v>
+        <v>-20732000</v>
       </c>
       <c r="K5" t="n">
-        <v>-56700000</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>-88200000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-88200000</v>
+      </c>
       <c r="M5" t="n">
-        <v>-42940000</v>
+        <v>-206268000</v>
       </c>
       <c r="N5" t="n">
-        <v>1084000</v>
+        <v>17466000</v>
       </c>
       <c r="O5" t="n">
-        <v>21890000</v>
+        <v>-42618000</v>
       </c>
       <c r="P5" t="n">
-        <v>40002000</v>
+        <v>30382000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-18112000</v>
+        <v>-73000000</v>
       </c>
       <c r="R5" t="n">
-        <v>-15840000</v>
+        <v>-107983000</v>
       </c>
       <c r="S5" t="n">
-        <v>-15840000</v>
+        <v>-107983000</v>
       </c>
       <c r="T5" t="n">
-        <v>-50074000</v>
+        <v>-73133000</v>
       </c>
       <c r="U5" t="n">
-        <v>8195000</v>
+        <v>15533000</v>
       </c>
       <c r="V5" t="n">
-        <v>-58269000</v>
+        <v>-88666000</v>
       </c>
       <c r="W5" t="n">
-        <v>284492000</v>
+        <v>558151000</v>
       </c>
       <c r="X5" t="n">
-        <v>-101146000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>5220000</v>
-      </c>
+        <v>-116204000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>-54678000</v>
+        <v>183092000</v>
       </c>
       <c r="AA5" t="n">
-        <v>31517000</v>
+        <v>-150818000</v>
       </c>
       <c r="AB5" t="n">
-        <v>175411000</v>
+        <v>187054000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-217234000</v>
+        <v>103188000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-44372000</v>
+        <v>43668000</v>
       </c>
       <c r="AE5" t="n">
-        <v>17090000</v>
+        <v>5365000</v>
       </c>
       <c r="AF5" t="n">
-        <v>103003000</v>
+        <v>140320000</v>
       </c>
       <c r="AG5" t="n">
-        <v>103003000</v>
+        <v>140320000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-277000</v>
+        <v>525000</v>
       </c>
       <c r="AI5" t="n">
-        <v>320500000</v>
+        <v>345053000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>168763000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-121017000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>378771000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>643115000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-2030000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-262314000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-300997000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-121601000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-23636000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-88200000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-88200000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-251097000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>14765000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4691000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>77210000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-72519000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-158200000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-158200000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-112353000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>8664000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-121017000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>289780000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-113092000</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>-96954000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-113198000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>165342000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-225000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-148873000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>14320000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>159268000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>159268000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2041000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>324197000</v>
       </c>
     </row>
   </sheetData>
@@ -3102,7 +3279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:ET2"/>
+  <dimension ref="A1:EP2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3273,585 +3450,565 @@
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>dividendRate</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>dividendYield</t>
+          <t>trailingPE</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>exDividendDate</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>payoutRatio</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>trailingPE</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>priceToSalesTrailing12Months</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>enterpriseValue</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>floatShares</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>enterpriseValue</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>floatShares</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>earningsQuarterlyGrowth</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>enterpriseToRevenue</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>earningsQuarterlyGrowth</t>
+          <t>enterpriseToEbitda</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>enterpriseToRevenue</t>
+          <t>lastDividendValue</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>enterpriseToEbitda</t>
+          <t>lastDividendDate</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>lastDividendValue</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>lastDividendDate</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>earningsGrowth</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>earningsGrowth</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>language</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>region</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="DB1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="DC1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>sourceInterval</t>
         </is>
       </c>
       <c r="DD1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>exchangeDataDelayedBy</t>
         </is>
       </c>
       <c r="DE1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="DF1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>marketState</t>
         </is>
       </c>
       <c r="DG1" t="inlineStr">
         <is>
-          <t>marketState</t>
+          <t>regularMarketChangePercent</t>
         </is>
       </c>
       <c r="DH1" t="inlineStr">
         <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
       <c r="DK1" t="inlineStr">
         <is>
-          <t>regularMarketPrice</t>
+          <t>exchange</t>
         </is>
       </c>
       <c r="DL1" t="inlineStr">
         <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>earningsCallTimestampStart</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>earningsCallTimestampEnd</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
       <c r="EO1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekRange</t>
+          <t>shortName</t>
         </is>
       </c>
       <c r="EP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -3947,7 +4104,7 @@
         <v>7</v>
       </c>
       <c r="U2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="V2" t="n">
         <v>1640908800</v>
@@ -3964,7 +4121,7 @@
         <v>2</v>
       </c>
       <c r="Z2" t="n">
-        <v>33.44</v>
+        <v>31.54</v>
       </c>
       <c r="AA2" t="n">
         <v>30.74</v>
@@ -3976,7 +4133,7 @@
         <v>30.74</v>
       </c>
       <c r="AD2" t="n">
-        <v>33.44</v>
+        <v>31.54</v>
       </c>
       <c r="AE2" t="n">
         <v>30.74</v>
@@ -3988,396 +4145,384 @@
         <v>30.74</v>
       </c>
       <c r="AH2" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>18.566845</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>47</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>4374720000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3812760000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.6713267000000001</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>29.8876</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>35.1932</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>0.7</v>
       </c>
-      <c r="AI2" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AJ2" t="n">
+      <c r="BA2" t="n">
+        <v>0.02219404</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4750274048</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.03612</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>81840780</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>126000000</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.39418998</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>126000000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>16.659</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>2.0841587</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1798675200</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1774915200</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>235380992</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>-0.20020801</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BX2" t="n">
         <v>1781740800</v>
       </c>
-      <c r="AK2" t="n">
-        <v>0.4094</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>19.567251</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>31</v>
-      </c>
-      <c r="AQ2" t="n">
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="BZ2" t="n">
+        <v>34.72</v>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="CB2" t="n">
+        <v>372631008</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>2.957</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>415225984</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>634985024</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>6516529152</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>30.219</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>51.718</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.04917</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>0.1157</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>1216297984</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>204596992</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>321505984</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>0.18665001</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>0.06372</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0.04147</v>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>1BC8.MI</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>en-US</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>Delayed Quote</t>
+        </is>
+      </c>
+      <c r="DA2" t="b">
         <v>0</v>
       </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>32.44</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>34.52</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>4215959808</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4278960000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>26.14</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>26.14</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0.646964</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>29.01</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>35.8012</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0.020933015</v>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="BG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>4480633856</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0.03612</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>81840780</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>126000000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.35047</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.39616</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>126000000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>16.659</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>2.0085237</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>1767139200</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1798675200</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>1774915200</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>235380992</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>10.791</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>-0.20020801</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0.27449715</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>1781740800</v>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="CD2" t="n">
-        <v>33.46</v>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="CF2" t="n">
-        <v>372631008</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>2.957</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>415225984</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>634985024</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>0.914</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>6516529152</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>30.219</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>51.718</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>0.04917</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>0.1157</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>1216297984</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>204596992</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>321505984</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>0.18665001</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>0.06372</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>0.04147</v>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>1BC8.MI</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>en-US</t>
-        </is>
-      </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>Delayed Quote</t>
-        </is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>20</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>15</v>
       </c>
       <c r="DE2" t="b">
         <v>0</v>
       </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>10.082436</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>34.72</v>
+      </c>
+      <c r="DI2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DI2" t="n">
+      <c r="DJ2" t="n">
         <v>1779113638</v>
       </c>
-      <c r="DJ2" t="n">
-        <v>0.059809983</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>33.46</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>1778254200</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>1778254200</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>1778254200</v>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>finmb_4975204</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>Europe/Rome</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
       </c>
       <c r="DO2" t="n">
-        <v>1746772200</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>1746772200</v>
+        <v>7200000</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>it_market</t>
+        </is>
       </c>
       <c r="DQ2" t="b">
         <v>0</v>
       </c>
-      <c r="DR2" t="n">
-        <v>1.71</v>
+      <c r="DR2" t="b">
+        <v>0</v>
       </c>
       <c r="DS2" t="n">
-        <v>4.449999</v>
+        <v>1746169200000</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.15339534</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-2.3412018</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.06539450600000001</v>
+        <v>3.1800003</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>30.74 - 30.74</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>Milan</t>
+        </is>
       </c>
       <c r="DW2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="DX2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DY2" t="b">
+        <v>8.580002</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0.32823268</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>26.14 - 44.5</t>
+        </is>
+      </c>
+      <c r="EA2" t="n">
+        <v>-9.779999</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-0.21977526</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>-20.020802</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>1778254200</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>1778254200</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>1778254200</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>1746772200</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>1746772200</v>
+      </c>
+      <c r="EI2" t="b">
         <v>0</v>
       </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>finmb_4975204</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>Europe/Rome</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="ED2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>it_market</t>
-        </is>
-      </c>
-      <c r="EF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>1746169200000</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>0.020000458</v>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>30.74 - 30.74</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>Milan</t>
-        </is>
+      <c r="EJ2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>4.8324013</v>
       </c>
       <c r="EL2" t="n">
-        <v>31</v>
+        <v>0.16168582</v>
       </c>
       <c r="EM2" t="n">
-        <v>7.3199997</v>
+        <v>-0.47319794</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.2800306</v>
+        <v>-0.013445721</v>
       </c>
       <c r="EO2" t="inlineStr">
         <is>
-          <t>26.14 - 44.5</t>
-        </is>
-      </c>
-      <c r="EP2" t="n">
-        <v>-11.040001</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>-0.24808991</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>-20.020802</v>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
           <t>Bechtle</t>
         </is>
       </c>
-      <c r="ET2" t="inlineStr"/>
+      <c r="EP2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
